--- a/backend/app/face_analysis/makeup.xlsx
+++ b/backend/app/face_analysis/makeup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai_exam\pj_styleflow\backend\app\face_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639229BD-CC1D-4024-AB21-8054296FF0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBB4F42-1927-4931-8FE9-FED7F4052A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{A6C25819-9308-4569-AA74-AF79C4674B86}"/>
   </bookViews>
